--- a/resources/reselling/files/reselling-adv-consignment-screen.xlsx
+++ b/resources/reselling/files/reselling-adv-consignment-screen.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,11 +77,6 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -127,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,8 +164,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,10 +529,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="73" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -581,7 +574,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Per-item costs off the top (postage + packing + allowance + per-order)</t>
+          <t>Per-item costs off the top (shipping + packing + allowance + per-order)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -1172,10 +1165,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="18" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/reselling/files/reselling-adv-consignment-screen.xlsx
+++ b/resources/reselling/files/reselling-adv-consignment-screen.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,10 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -122,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,6 +168,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -529,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="73" customWidth="1" min="1" max="1"/>
@@ -1161,9 +1166,13 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — Free resources: eports.global/resources/reselling</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — Free resources: eports.global/resources/reselling</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
